--- a/src/DOO/ex02_DOO_glossary.xlsx
+++ b/src/DOO/ex02_DOO_glossary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Waysy\Documents\GitHub\pim_01\Exercises\DOO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Waysy\Documents\GitHub\pim_02\scr\DOO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A400E7DD-E126-436E-A3D7-B2B96DEDF054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2EE1F3-3709-4B3F-8A7D-A0303E03E8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Глоссарий</t>
   </si>
@@ -100,6 +100,54 @@
   </si>
   <si>
     <t>Дата добавления</t>
+  </si>
+  <si>
+    <t>Стартап</t>
+  </si>
+  <si>
+    <t>Онлайн-система доставки</t>
+  </si>
+  <si>
+    <t>Программно-аппаратный комплекс, предназначенный для автоматизации процессов приема, обработки, распределения и контроля выполнения заказов доставки. Доступ к системе осуществляется через интернет.</t>
+  </si>
+  <si>
+    <t>Заказ</t>
+  </si>
+  <si>
+    <t>Оператор</t>
+  </si>
+  <si>
+    <t>Диспетчер</t>
+  </si>
+  <si>
+    <t>Роль пользователя в системе, отвечающая за мониторинг работы курьеров, контроль выполнения заказов в реальном времени, решение оперативных проблем и переназначение заказов между курьерами в случае необходимости.</t>
+  </si>
+  <si>
+    <t>Администратор системы</t>
+  </si>
+  <si>
+    <t>Статус заказа</t>
+  </si>
+  <si>
+    <t>Бронирование заказа</t>
+  </si>
+  <si>
+    <t>Действие, совершаемое курьером в системе, в результате которого заказ переходит из статуса "Свободный" в статус "Назначен курьеру" и закрепляется за конкретным курьером для выполнения.</t>
+  </si>
+  <si>
+    <t>Молодая компания, находящаяся на стадии развития и строящая свой бизнес на основе инновационных идей или новых технологий.</t>
+  </si>
+  <si>
+    <t>Базовая сущность системы, содержащая информацию о товаре, точках отправления и назначения, получателе и сроках доставки.</t>
+  </si>
+  <si>
+    <t>Роль пользователя в системе, отвечающая за ручной ввод и первичную обработку заказов, поступивших от магазинов и предприятий питания по различным каналам.</t>
+  </si>
+  <si>
+    <t>Роль пользователя, наделенная максимальными правами для управления учетными записями других пользователей, назначения ролей и обеспечения общей работоспособности системы.</t>
+  </si>
+  <si>
+    <t>Поле, отражающее текущее состояние заказа в процессе его выполнения.</t>
   </si>
 </sst>
 </file>
@@ -115,27 +163,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="14"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="204"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF0F1115"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -158,7 +205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -167,6 +214,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -449,141 +499,259 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.453125" customWidth="1"/>
+    <col min="1" max="1" width="37.1796875" customWidth="1"/>
     <col min="2" max="2" width="50.08984375" customWidth="1"/>
     <col min="3" max="3" width="23.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="66.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:3" ht="66.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="47" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
+      <c r="C3" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="47" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="35" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="36" x14ac:dyDescent="0.4">
+      <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="35" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
+      <c r="C5" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="36" x14ac:dyDescent="0.4">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="87.5" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="90" x14ac:dyDescent="0.4">
+      <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="87.5" x14ac:dyDescent="0.45">
-      <c r="A8" s="2" t="s">
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="90" x14ac:dyDescent="0.4">
+      <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="70" x14ac:dyDescent="0.45">
-      <c r="A9" s="2" t="s">
+      <c r="C8" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="72" x14ac:dyDescent="0.4">
+      <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="52.5" x14ac:dyDescent="0.45">
-      <c r="A10" s="2" t="s">
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="72" x14ac:dyDescent="0.4">
+      <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="105" x14ac:dyDescent="0.45">
-      <c r="A11" s="2" t="s">
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="108" x14ac:dyDescent="0.4">
+      <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="52.5" x14ac:dyDescent="0.45">
-      <c r="A12" s="2" t="s">
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="54" x14ac:dyDescent="0.4">
+      <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="1">
-        <v>2</v>
-      </c>
+      <c r="C12" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="72" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="108" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="72" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="90" x14ac:dyDescent="0.4">
+      <c r="A16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="108" x14ac:dyDescent="0.4">
+      <c r="A17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="90" x14ac:dyDescent="0.4">
+      <c r="A18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="36" x14ac:dyDescent="0.4">
+      <c r="A19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="90" x14ac:dyDescent="0.4">
+      <c r="A20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+    </row>
+    <row r="24" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/DOO/ex02_DOO_glossary.xlsx
+++ b/src/DOO/ex02_DOO_glossary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Waysy\Documents\GitHub\pim_02\scr\DOO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Waysy\Documents\GitHub\pim_01\src\DOO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2EE1F3-3709-4B3F-8A7D-A0303E03E8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D693355A-A161-497A-810F-C7AE64874881}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15840" yWindow="3610" windowWidth="10850" windowHeight="13800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>Глоссарий</t>
   </si>
@@ -148,6 +148,36 @@
   </si>
   <si>
     <t>Поле, отражающее текущее состояние заказа в процессе его выполнения.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interview (интервью) </t>
+  </si>
+  <si>
+    <t>техника выявления потребностей, болей, требований через непосредственное общение, задавание подходящих вопросов и документирования ответов.</t>
+  </si>
+  <si>
+    <t>Survey/Questionnaire (опрос/анкетирование)</t>
+  </si>
+  <si>
+    <t>техника выявления требований систематическим способом за короткое время. Группе респондентов задаются одинаковые вопросы (открытые или закрытые), и ответы анализируются.</t>
+  </si>
+  <si>
+    <t>Role-playing game (ролевая игра)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> техника, поощряющая участников к совместному достижению цели игры, например, пониманию проблем и возможностей, нахождению решения.</t>
+  </si>
+  <si>
+    <t>Brainstorming (мозговой штурм)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> эффективный способ решения проблем, применяется, когда решения нет совсем или имеющееся решение неоднозначно. </t>
+  </si>
+  <si>
+    <t>Seminar (семинар)</t>
+  </si>
+  <si>
+    <t>мероприятие, применяемое группой для достижения выбранной цели и выработки согласия по этой цели.</t>
   </si>
 </sst>
 </file>
@@ -723,29 +753,49 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="18" x14ac:dyDescent="0.4">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
+    <row r="21" spans="1:3" ht="72" x14ac:dyDescent="0.4">
+      <c r="A21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" ht="18" x14ac:dyDescent="0.4">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
+    <row r="22" spans="1:3" ht="90" x14ac:dyDescent="0.4">
+      <c r="A22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" ht="18" x14ac:dyDescent="0.4">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
+    <row r="23" spans="1:3" ht="72" x14ac:dyDescent="0.4">
+      <c r="A23" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="C23" s="4"/>
     </row>
-    <row r="24" spans="1:3" ht="18" x14ac:dyDescent="0.4">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
+    <row r="24" spans="1:3" ht="54" x14ac:dyDescent="0.4">
+      <c r="A24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" ht="18" x14ac:dyDescent="0.4">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
+    <row r="25" spans="1:3" ht="54" x14ac:dyDescent="0.4">
+      <c r="A25" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="C25" s="2"/>
     </row>
     <row r="26" spans="1:3" ht="18" x14ac:dyDescent="0.4">
